--- a/exports/trend_1d/JSWSTEEL_full_report.xlsx
+++ b/exports/trend_1d/JSWSTEEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.08</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42073</v>
+        <v>42074</v>
       </c>
       <c r="H2" t="n">
-        <v>94.45999999999999</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>93.29364314284135</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.72</v>
+        <v>-4.15</v>
       </c>
       <c r="L2" t="n">
         <v>5.05</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.89</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42116</v>
+        <v>42117</v>
       </c>
       <c r="H3" t="n">
-        <v>96.05</v>
+        <v>98.56</v>
       </c>
       <c r="I3" t="n">
         <v>98.23040297567078</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.2</v>
+        <v>-5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>5.57</v>
+        <v>6.69</v>
       </c>
       <c r="M3" t="n">
         <v>1.44</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42130</v>
+        <v>42131</v>
       </c>
       <c r="H4" t="n">
-        <v>93.05</v>
+        <v>88.59</v>
       </c>
       <c r="I4" t="n">
         <v>88.98245695503995</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.59</v>
+        <v>-10.12</v>
       </c>
       <c r="L4" t="n">
-        <v>6.34</v>
+        <v>11.22</v>
       </c>
       <c r="M4" t="n">
         <v>0.65</v>
       </c>
       <c r="N4" t="n">
-        <v>4.39</v>
+        <v>4.79</v>
       </c>
       <c r="O4" t="n">
         <v>2.61</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.18</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42220</v>
+        <v>42221</v>
       </c>
       <c r="H5" t="n">
-        <v>87.98</v>
+        <v>88.63</v>
       </c>
       <c r="I5" t="n">
         <v>88.4849872848132</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="L5" t="n">
         <v>5.43</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.35</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42275</v>
+        <v>42276</v>
       </c>
       <c r="H6" t="n">
-        <v>86.5</v>
+        <v>84.02</v>
       </c>
       <c r="I6" t="n">
         <v>85.87115770072366</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.4</v>
+        <v>-5.2</v>
       </c>
       <c r="L6" t="n">
         <v>6.5</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>14.19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42338</v>
+        <v>42339</v>
       </c>
       <c r="H7" t="n">
-        <v>90.22</v>
+        <v>94.38</v>
       </c>
       <c r="I7" t="n">
         <v>94.05718157661741</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.38</v>
+        <v>-12.33</v>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>12.91</v>
       </c>
       <c r="M7" t="n">
         <v>2.12</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.95</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H8" t="n">
-        <v>100.35</v>
+        <v>97.25</v>
       </c>
       <c r="I8" t="n">
         <v>98.12548568397966</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K8" t="n">
-        <v>6.33</v>
+        <v>3.04</v>
       </c>
       <c r="L8" t="n">
         <v>5.57</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>12.49</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42391</v>
+        <v>42394</v>
       </c>
       <c r="H9" t="n">
-        <v>106.8</v>
+        <v>110.73</v>
       </c>
       <c r="I9" t="n">
         <v>109.3965623445723</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.82</v>
+        <v>-13.86</v>
       </c>
       <c r="L9" t="n">
-        <v>10.39</v>
+        <v>14.63</v>
       </c>
       <c r="M9" t="n">
         <v>1.14</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>13.35</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42402</v>
+        <v>42403</v>
       </c>
       <c r="H10" t="n">
-        <v>100.33</v>
+        <v>97.34</v>
       </c>
       <c r="I10" t="n">
         <v>99.36995397793433</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.390000000000001</v>
+        <v>-12.09</v>
       </c>
       <c r="L10" t="n">
-        <v>9.779999999999999</v>
+        <v>13.45</v>
       </c>
       <c r="M10" t="n">
-        <v>1.47</v>
+        <v>1.88</v>
       </c>
       <c r="N10" t="n">
         <v>4.5</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>16.35</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42429</v>
+        <v>42430</v>
       </c>
       <c r="H11" t="n">
-        <v>112.65</v>
+        <v>114.35</v>
       </c>
       <c r="I11" t="n">
         <v>112.9592023466959</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>-15.73</v>
+        <v>-17.47</v>
       </c>
       <c r="L11" t="n">
-        <v>17.63</v>
+        <v>18.41</v>
       </c>
       <c r="M11" t="n">
         <v>2.69</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.87</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42499</v>
+        <v>42500</v>
       </c>
       <c r="H12" t="n">
-        <v>132.62</v>
+        <v>128.78</v>
       </c>
       <c r="I12" t="n">
         <v>129.1085718438716</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K12" t="n">
-        <v>15.98</v>
+        <v>12.62</v>
       </c>
       <c r="L12" t="n">
         <v>1.53</v>
@@ -1125,7 +1268,7 @@
         <v>1.79</v>
       </c>
       <c r="N12" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.51</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>7.54</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42516</v>
+        <v>42517</v>
       </c>
       <c r="H13" t="n">
-        <v>131.9</v>
+        <v>137.57</v>
       </c>
       <c r="I13" t="n">
         <v>135.5144415099257</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.42</v>
+        <v>-6.83</v>
       </c>
       <c r="L13" t="n">
-        <v>4.36</v>
+        <v>7.16</v>
       </c>
       <c r="M13" t="n">
         <v>1.16</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
         <v>-2.9</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.4</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42622</v>
+        <v>42625</v>
       </c>
       <c r="H14" t="n">
-        <v>182.38</v>
+        <v>174.51</v>
       </c>
       <c r="I14" t="n">
         <v>174.6826062610897</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K14" t="n">
-        <v>32.57</v>
+        <v>26.85</v>
       </c>
       <c r="L14" t="n">
         <v>4.55</v>
@@ -1239,7 +1406,7 @@
         <v>1.81</v>
       </c>
       <c r="N14" t="n">
-        <v>3.16</v>
+        <v>4.32</v>
       </c>
       <c r="O14" t="n">
         <v>4.3</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H15" t="n">
-        <v>168.09</v>
+        <v>175.64</v>
       </c>
       <c r="I15" t="n">
         <v>172.9331307947186</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K15" t="n">
-        <v>3.68</v>
+        <v>-0.65</v>
       </c>
       <c r="L15" t="n">
         <v>4.58</v>
@@ -1296,7 +1475,7 @@
         <v>1.52</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>4.49</v>
       </c>
       <c r="O15" t="n">
         <v>-4.32</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.71</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H16" t="n">
-        <v>156.81</v>
+        <v>153.27</v>
       </c>
       <c r="I16" t="n">
         <v>155.0651913855851</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.72</v>
+        <v>-12.74</v>
       </c>
       <c r="L16" t="n">
-        <v>12.2</v>
+        <v>13.93</v>
       </c>
       <c r="M16" t="n">
         <v>1.21</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>7.86</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H17" t="n">
-        <v>163.05</v>
+        <v>175.65</v>
       </c>
       <c r="I17" t="n">
         <v>165.31672146323</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.38</v>
+        <v>-14.6</v>
       </c>
       <c r="L17" t="n">
-        <v>8.789999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="M17" t="n">
         <v>1.39</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>7.73</v>
       </c>
       <c r="O17" t="n">
         <v>-2.26</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.53</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42801</v>
+        <v>42802</v>
       </c>
       <c r="H18" t="n">
-        <v>181.45</v>
+        <v>178.05</v>
       </c>
       <c r="I18" t="n">
         <v>179.5008621307993</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="L18" t="n">
         <v>6.92</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>10.04</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42809</v>
+        <v>42810</v>
       </c>
       <c r="H19" t="n">
-        <v>183.5</v>
+        <v>192.45</v>
       </c>
       <c r="I19" t="n">
         <v>192.2518194222711</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.06</v>
+        <v>-8.09</v>
       </c>
       <c r="L19" t="n">
-        <v>3.85</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>2.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.21</v>
+        <v>4.88</v>
       </c>
       <c r="O19" t="n">
         <v>-1.87</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.43</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H20" t="n">
-        <v>246.95</v>
+        <v>236.85</v>
       </c>
       <c r="I20" t="n">
         <v>246.8580980121181</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K20" t="n">
-        <v>28.32</v>
+        <v>23.07</v>
       </c>
       <c r="L20" t="n">
         <v>7.66</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.5</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43034</v>
+        <v>43035</v>
       </c>
       <c r="H21" t="n">
-        <v>259.95</v>
+        <v>265.3</v>
       </c>
       <c r="I21" t="n">
         <v>263.7700366204612</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.75</v>
+        <v>-12.01</v>
       </c>
       <c r="L21" t="n">
-        <v>12.03</v>
+        <v>13.72</v>
       </c>
       <c r="M21" t="n">
         <v>1.43</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.15</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43074</v>
+        <v>43075</v>
       </c>
       <c r="H22" t="n">
-        <v>247.7</v>
+        <v>242.15</v>
       </c>
       <c r="I22" t="n">
         <v>246.7713125874139</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.63</v>
+        <v>-8.73</v>
       </c>
       <c r="L22" t="n">
-        <v>7.84</v>
+        <v>9.1</v>
       </c>
       <c r="M22" t="n">
         <v>0.92</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.93</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H23" t="n">
-        <v>262.1</v>
+        <v>265.3</v>
       </c>
       <c r="I23" t="n">
         <v>263.7747370918372</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.24</v>
+        <v>-9.56</v>
       </c>
       <c r="L23" t="n">
-        <v>9.23</v>
+        <v>9.85</v>
       </c>
       <c r="M23" t="n">
         <v>2.29</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.69</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43175</v>
+        <v>43178</v>
       </c>
       <c r="H24" t="n">
-        <v>290.25</v>
+        <v>283.6</v>
       </c>
       <c r="I24" t="n">
         <v>284.3925333769797</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K24" t="n">
-        <v>9.4</v>
+        <v>6.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.58</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>10.57</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H25" t="n">
-        <v>309.4</v>
+        <v>311.35</v>
       </c>
       <c r="I25" t="n">
         <v>309.4863119054537</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K25" t="n">
-        <v>-9.1</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>10.37</v>
+        <v>10.98</v>
       </c>
       <c r="M25" t="n">
         <v>1.89</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43280</v>
+        <v>43283</v>
       </c>
       <c r="H26" t="n">
-        <v>326.8</v>
+        <v>313.4</v>
       </c>
       <c r="I26" t="n">
         <v>317.7501954732187</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K26" t="n">
-        <v>4.96</v>
+        <v>0.66</v>
       </c>
       <c r="L26" t="n">
         <v>1.88</v>
@@ -1923,7 +2234,7 @@
         <v>1.34</v>
       </c>
       <c r="N26" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0.63</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>10.95</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43311</v>
+        <v>43312</v>
       </c>
       <c r="H27" t="n">
-        <v>327.85</v>
+        <v>330.4</v>
       </c>
       <c r="I27" t="n">
         <v>329.5466738103972</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.61</v>
+        <v>-5.42</v>
       </c>
       <c r="L27" t="n">
-        <v>4.95</v>
+        <v>6.21</v>
       </c>
       <c r="M27" t="n">
         <v>1.18</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43377</v>
+        <v>43378</v>
       </c>
       <c r="H28" t="n">
-        <v>377.6</v>
+        <v>366.6</v>
       </c>
       <c r="I28" t="n">
         <v>377.1370895411092</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K28" t="n">
-        <v>14.29</v>
+        <v>10.96</v>
       </c>
       <c r="L28" t="n">
         <v>2.59</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>14.41</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H29" t="n">
-        <v>282.1</v>
+        <v>291.2</v>
       </c>
       <c r="I29" t="n">
         <v>290.4200213975403</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K29" t="n">
-        <v>23.05</v>
+        <v>20.57</v>
       </c>
       <c r="L29" t="n">
         <v>5.07</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>11.58</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H30" t="n">
-        <v>287.35</v>
+        <v>276.9</v>
       </c>
       <c r="I30" t="n">
         <v>279.9189984848517</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.32</v>
+        <v>-4.91</v>
       </c>
       <c r="L30" t="n">
-        <v>5.22</v>
+        <v>6.1</v>
       </c>
       <c r="M30" t="n">
         <v>2.54</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.12</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H31" t="n">
-        <v>219.55</v>
+        <v>238.1</v>
       </c>
       <c r="I31" t="n">
         <v>237.9117459660031</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K31" t="n">
-        <v>20.71</v>
+        <v>14.01</v>
       </c>
       <c r="L31" t="n">
         <v>7.44</v>
@@ -2208,7 +2579,7 @@
         <v>2.55</v>
       </c>
       <c r="N31" t="n">
-        <v>4.86</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O31" t="n">
         <v>-3.64</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>16.72</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43742</v>
+        <v>43745</v>
       </c>
       <c r="H32" t="n">
-        <v>214.65</v>
+        <v>208</v>
       </c>
       <c r="I32" t="n">
         <v>212.6718100076847</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.85</v>
+        <v>-12.64</v>
       </c>
       <c r="L32" t="n">
-        <v>10.77</v>
+        <v>13.06</v>
       </c>
       <c r="M32" t="n">
         <v>1.81</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>15.63</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43770</v>
+        <v>43773</v>
       </c>
       <c r="H33" t="n">
-        <v>237.6</v>
+        <v>250.2</v>
       </c>
       <c r="I33" t="n">
         <v>238.3965690206844</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K33" t="n">
-        <v>-14.23</v>
+        <v>-20.29</v>
       </c>
       <c r="L33" t="n">
-        <v>15.14</v>
+        <v>22.52</v>
       </c>
       <c r="M33" t="n">
         <v>1.18</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.24</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43857</v>
+        <v>43858</v>
       </c>
       <c r="H34" t="n">
-        <v>262.8</v>
+        <v>255.25</v>
       </c>
       <c r="I34" t="n">
         <v>258.3111023826893</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K34" t="n">
-        <v>5.04</v>
+        <v>2.02</v>
       </c>
       <c r="L34" t="n">
         <v>4.6</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.92</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43866</v>
+        <v>43867</v>
       </c>
       <c r="H35" t="n">
-        <v>269.25</v>
+        <v>276.45</v>
       </c>
       <c r="I35" t="n">
         <v>274.975428264184</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.48</v>
+        <v>-8.31</v>
       </c>
       <c r="L35" t="n">
-        <v>6.43</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>1.47</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>11.92</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43881</v>
+        <v>43885</v>
       </c>
       <c r="H36" t="n">
-        <v>281.8</v>
+        <v>258.95</v>
       </c>
       <c r="I36" t="n">
         <v>265.1682458352804</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K36" t="n">
-        <v>1.94</v>
+        <v>-6.33</v>
       </c>
       <c r="L36" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="M36" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="N36" t="n">
-        <v>1.43</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O36" t="n">
         <v>2.67</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>15.3</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H37" t="n">
-        <v>184.2</v>
+        <v>193.95</v>
       </c>
       <c r="I37" t="n">
         <v>187.5539504440457</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K37" t="n">
-        <v>28.87</v>
+        <v>25.1</v>
       </c>
       <c r="L37" t="n">
         <v>7.34</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>15.52</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H38" t="n">
-        <v>268.2</v>
+        <v>258.55</v>
       </c>
       <c r="I38" t="n">
         <v>266.3117996470419</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K38" t="n">
-        <v>38.28</v>
+        <v>33.31</v>
       </c>
       <c r="L38" t="n">
         <v>9.539999999999999</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.92</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44111</v>
+        <v>44112</v>
       </c>
       <c r="H39" t="n">
-        <v>291.45</v>
+        <v>292.95</v>
       </c>
       <c r="I39" t="n">
         <v>291.9523871746054</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.72</v>
+        <v>-13.3</v>
       </c>
       <c r="L39" t="n">
-        <v>14.1</v>
+        <v>15.41</v>
       </c>
       <c r="M39" t="n">
         <v>1.33</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H40" t="n">
-        <v>376.3</v>
+        <v>366.85</v>
       </c>
       <c r="I40" t="n">
         <v>371.5760420210528</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K40" t="n">
-        <v>28.45</v>
+        <v>25.23</v>
       </c>
       <c r="L40" t="n">
         <v>4.64</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>13.94</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44251</v>
+        <v>44252</v>
       </c>
       <c r="H41" t="n">
-        <v>408.1</v>
+        <v>421.75</v>
       </c>
       <c r="I41" t="n">
         <v>417.9732933705956</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>-11.24</v>
+        <v>-14.97</v>
       </c>
       <c r="L41" t="n">
         <v>16.29</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.8</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="H42" t="n">
-        <v>698.2</v>
+        <v>681.45</v>
       </c>
       <c r="I42" t="n">
         <v>683.5912021061838</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K42" t="n">
-        <v>65.55</v>
+        <v>61.58</v>
       </c>
       <c r="L42" t="n">
         <v>7.04</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.68</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44405</v>
+        <v>44406</v>
       </c>
       <c r="H43" t="n">
-        <v>721.7</v>
+        <v>748.4</v>
       </c>
       <c r="I43" t="n">
         <v>724.6319800544383</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.91</v>
+        <v>-9.82</v>
       </c>
       <c r="L43" t="n">
-        <v>8.18</v>
+        <v>11.25</v>
       </c>
       <c r="M43" t="n">
         <v>2.34</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H44" t="n">
-        <v>737.45</v>
+        <v>684.6</v>
       </c>
       <c r="I44" t="n">
         <v>702.8362952932389</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.46</v>
+        <v>-8.52</v>
       </c>
       <c r="L44" t="n">
-        <v>3.85</v>
+        <v>8.94</v>
       </c>
       <c r="M44" t="n">
-        <v>0.54</v>
+        <v>2.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.37</v>
+        <v>7.17</v>
       </c>
       <c r="O44" t="n">
         <v>3.7</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>13.88</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44483</v>
+        <v>44487</v>
       </c>
       <c r="H45" t="n">
-        <v>692.85</v>
+        <v>715.8</v>
       </c>
       <c r="I45" t="n">
         <v>707.5926301664135</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.21</v>
+        <v>-4.56</v>
       </c>
       <c r="L45" t="n">
-        <v>5.46</v>
+        <v>6.24</v>
       </c>
       <c r="M45" t="n">
         <v>1.67</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H46" t="n">
-        <v>680.9</v>
+        <v>628.65</v>
       </c>
       <c r="I46" t="n">
         <v>648.6629042226635</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.88</v>
+        <v>-12.18</v>
       </c>
       <c r="L46" t="n">
-        <v>10.17</v>
+        <v>12.79</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.86</v>
       </c>
       <c r="N46" t="n">
-        <v>3.39</v>
+        <v>7.67</v>
       </c>
       <c r="O46" t="n">
         <v>3.31</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>14.36</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H47" t="n">
-        <v>670.4</v>
+        <v>694.5</v>
       </c>
       <c r="I47" t="n">
         <v>689.3891805673661</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.64</v>
+        <v>-10.47</v>
       </c>
       <c r="L47" t="n">
-        <v>10.23</v>
+        <v>10.87</v>
       </c>
       <c r="M47" t="n">
         <v>1.08</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>9.56</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H48" t="n">
-        <v>666.25</v>
+        <v>621.8</v>
       </c>
       <c r="I48" t="n">
         <v>631.1709006143958</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.07</v>
+        <v>-10.47</v>
       </c>
       <c r="L48" t="n">
-        <v>7.38</v>
+        <v>11.02</v>
       </c>
       <c r="M48" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="N48" t="n">
-        <v>3.93</v>
+        <v>6.67</v>
       </c>
       <c r="O48" t="n">
         <v>3.59</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>13.75</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44622</v>
+        <v>44623</v>
       </c>
       <c r="H49" t="n">
-        <v>644.6</v>
+        <v>654.7</v>
       </c>
       <c r="I49" t="n">
         <v>653.2256262968111</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.67</v>
+        <v>-5.29</v>
       </c>
       <c r="L49" t="n">
         <v>9.039999999999999</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>11.45</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H50" t="n">
-        <v>707.75</v>
+        <v>690.4</v>
       </c>
       <c r="I50" t="n">
         <v>699.8254335249062</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K50" t="n">
-        <v>8.1</v>
+        <v>5.45</v>
       </c>
       <c r="L50" t="n">
         <v>6.35</v>
       </c>
       <c r="M50" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="N50" t="n">
         <v>4.82</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.09</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44769</v>
+        <v>44770</v>
       </c>
       <c r="H51" t="n">
-        <v>602.7</v>
+        <v>616.7</v>
       </c>
       <c r="I51" t="n">
         <v>608.5069918380719</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K51" t="n">
-        <v>12.7</v>
+        <v>10.67</v>
       </c>
       <c r="L51" t="n">
         <v>1.52</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H52" t="n">
-        <v>669</v>
+        <v>646.15</v>
       </c>
       <c r="I52" t="n">
         <v>648.0643308934154</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K52" t="n">
-        <v>8.48</v>
+        <v>4.78</v>
       </c>
       <c r="L52" t="n">
         <v>2.21</v>
@@ -3405,7 +4028,7 @@
         <v>1.95</v>
       </c>
       <c r="N52" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="O52" t="n">
         <v>2.32</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>8.44</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H53" t="n">
-        <v>643.2</v>
+        <v>674.45</v>
       </c>
       <c r="I53" t="n">
         <v>673.2358089437671</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>0.46</v>
+        <v>-4.38</v>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>4.93</v>
       </c>
       <c r="M53" t="n">
         <v>1.64</v>
       </c>
       <c r="N53" t="n">
-        <v>3.15</v>
+        <v>4.86</v>
       </c>
       <c r="O53" t="n">
         <v>-3.42</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.02</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44949</v>
+        <v>44950</v>
       </c>
       <c r="H54" t="n">
-        <v>733.95</v>
+        <v>722.05</v>
       </c>
       <c r="I54" t="n">
         <v>726.5804978464797</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K54" t="n">
-        <v>8.82</v>
+        <v>7.06</v>
       </c>
       <c r="L54" t="n">
         <v>8.81</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45026</v>
+        <v>45027</v>
       </c>
       <c r="H55" t="n">
-        <v>688.5</v>
+        <v>713.6</v>
       </c>
       <c r="I55" t="n">
         <v>701.4876012658278</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K55" t="n">
-        <v>4.65</v>
+        <v>1.17</v>
       </c>
       <c r="L55" t="n">
         <v>2.31</v>
@@ -3576,7 +4235,7 @@
         <v>1.33</v>
       </c>
       <c r="N55" t="n">
-        <v>2.86</v>
+        <v>3.65</v>
       </c>
       <c r="O55" t="n">
         <v>-1.62</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45063</v>
+        <v>45064</v>
       </c>
       <c r="H56" t="n">
-        <v>695.1</v>
+        <v>692.05</v>
       </c>
       <c r="I56" t="n">
         <v>693.6023896390336</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.59</v>
+        <v>-3.02</v>
       </c>
       <c r="L56" t="n">
         <v>3.52</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.46</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45084</v>
+        <v>45085</v>
       </c>
       <c r="H57" t="n">
-        <v>729.75</v>
+        <v>748.8</v>
       </c>
       <c r="I57" t="n">
         <v>733.3793388742022</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.45</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>5.8</v>
+        <v>10.46</v>
       </c>
       <c r="M57" t="n">
         <v>0.82</v>
       </c>
       <c r="N57" t="n">
-        <v>2.37</v>
+        <v>2.61</v>
       </c>
       <c r="O57" t="n">
         <v>-0.44</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>6.77</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45162</v>
+        <v>45163</v>
       </c>
       <c r="H58" t="n">
-        <v>787.9</v>
+        <v>773.15</v>
       </c>
       <c r="I58" t="n">
         <v>773.6182516395332</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K58" t="n">
-        <v>5.22</v>
+        <v>3.25</v>
       </c>
       <c r="L58" t="n">
         <v>2.8</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="N58" t="n">
         <v>2.58</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>6.84</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H59" t="n">
-        <v>815.75</v>
+        <v>824.25</v>
       </c>
       <c r="I59" t="n">
         <v>821.2229224722828</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.51</v>
+        <v>-6.61</v>
       </c>
       <c r="L59" t="n">
-        <v>6.91</v>
+        <v>7.27</v>
       </c>
       <c r="M59" t="n">
         <v>0.76</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>5.87</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45190</v>
+        <v>45191</v>
       </c>
       <c r="H60" t="n">
-        <v>778.35</v>
+        <v>774.05</v>
       </c>
       <c r="I60" t="n">
         <v>775.8737922202688</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.57</v>
+        <v>-6.09</v>
       </c>
       <c r="L60" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="M60" t="n">
         <v>0.09</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.72</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45250</v>
+        <v>45251</v>
       </c>
       <c r="H61" t="n">
-        <v>761.85</v>
+        <v>775.8</v>
       </c>
       <c r="I61" t="n">
         <v>774.6182868663177</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K61" t="n">
-        <v>1.58</v>
+        <v>-0.23</v>
       </c>
       <c r="L61" t="n">
         <v>3.48</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.57</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45296</v>
+        <v>45299</v>
       </c>
       <c r="H62" t="n">
-        <v>829.4</v>
+        <v>821.95</v>
       </c>
       <c r="I62" t="n">
         <v>825.8765761806363</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K62" t="n">
-        <v>6.91</v>
+        <v>5.95</v>
       </c>
       <c r="L62" t="n">
         <v>1.33</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>7.69</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H63" t="n">
-        <v>830.2</v>
+        <v>871.95</v>
       </c>
       <c r="I63" t="n">
         <v>845.067053583952</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K63" t="n">
-        <v>-1</v>
+        <v>-6.08</v>
       </c>
       <c r="L63" t="n">
-        <v>3.41</v>
+        <v>6.63</v>
       </c>
       <c r="M63" t="n">
         <v>1.18</v>
       </c>
       <c r="N63" t="n">
-        <v>4.51</v>
+        <v>5.03</v>
       </c>
       <c r="O63" t="n">
         <v>-0.9</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H64" t="n">
-        <v>931.45</v>
+        <v>889.45</v>
       </c>
       <c r="I64" t="n">
         <v>892.0517083531103</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K64" t="n">
-        <v>6.82</v>
+        <v>2.01</v>
       </c>
       <c r="L64" t="n">
         <v>5.52</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45504</v>
+        <v>45505</v>
       </c>
       <c r="H65" t="n">
-        <v>928.25</v>
+        <v>934.55</v>
       </c>
       <c r="I65" t="n">
         <v>930.8343302990165</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.36</v>
+        <v>-5.07</v>
       </c>
       <c r="L65" t="n">
-        <v>5.27</v>
+        <v>7.7</v>
       </c>
       <c r="M65" t="n">
         <v>1.04</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.37</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H66" t="n">
-        <v>899.55</v>
+        <v>863.8</v>
       </c>
       <c r="I66" t="n">
         <v>875.0046603017338</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.75</v>
+        <v>-7.57</v>
       </c>
       <c r="L66" t="n">
-        <v>4.12</v>
+        <v>8.6</v>
       </c>
       <c r="M66" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="N66" t="n">
-        <v>3.75</v>
+        <v>3.97</v>
       </c>
       <c r="O66" t="n">
         <v>0.68</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>9.75</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45527</v>
+        <v>45530</v>
       </c>
       <c r="H67" t="n">
-        <v>941.05</v>
+        <v>963.5</v>
       </c>
       <c r="I67" t="n">
         <v>948.0582251555957</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K67" t="n">
-        <v>-8.94</v>
+        <v>-11.54</v>
       </c>
       <c r="L67" t="n">
-        <v>9.279999999999999</v>
+        <v>12.17</v>
       </c>
       <c r="M67" t="n">
         <v>1.7</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.1</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H68" t="n">
-        <v>981.45</v>
+        <v>963.65</v>
       </c>
       <c r="I68" t="n">
         <v>969.4184938710482</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K68" t="n">
-        <v>1.86</v>
+        <v>0.02</v>
       </c>
       <c r="L68" t="n">
         <v>5.38</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45694</v>
+        <v>45695</v>
       </c>
       <c r="H69" t="n">
-        <v>948.4</v>
+        <v>980.75</v>
       </c>
       <c r="I69" t="n">
         <v>950.8811708310915</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K69" t="n">
-        <v>1.58</v>
+        <v>-1.77</v>
       </c>
       <c r="L69" t="n">
         <v>6.21</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>8.57</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H70" t="n">
-        <v>1005.75</v>
+        <v>930.3</v>
       </c>
       <c r="I70" t="n">
         <v>1002.526057284129</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K70" t="n">
-        <v>2.55</v>
+        <v>-5.14</v>
       </c>
       <c r="L70" t="n">
-        <v>4.35</v>
+        <v>7.7</v>
       </c>
       <c r="M70" t="n">
-        <v>1.64</v>
+        <v>9.92</v>
       </c>
       <c r="N70" t="n">
-        <v>3.67</v>
+        <v>7.5</v>
       </c>
       <c r="O70" t="n">
         <v>3.41</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>9.81</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H71" t="n">
-        <v>1007.2</v>
+        <v>1034</v>
       </c>
       <c r="I71" t="n">
         <v>1021.577163815883</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K71" t="n">
-        <v>-8.27</v>
+        <v>-11.15</v>
       </c>
       <c r="L71" t="n">
-        <v>9.18</v>
+        <v>12.2</v>
       </c>
       <c r="M71" t="n">
         <v>2.84</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,25 +5387,25 @@
         <v>10.08</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45779</v>
+        <v>45782</v>
       </c>
       <c r="H72" t="n">
-        <v>973.2</v>
+        <v>955.5</v>
       </c>
       <c r="I72" t="n">
         <v>957.599787557964</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.88</v>
+        <v>-7.59</v>
       </c>
       <c r="L72" t="n">
         <v>8.289999999999999</v>
       </c>
       <c r="M72" t="n">
-        <v>0.84</v>
+        <v>1.38</v>
       </c>
       <c r="N72" t="n">
         <v>5.5</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>11.39</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="H73" t="n">
-        <v>989.3</v>
+        <v>1038.3</v>
       </c>
       <c r="I73" t="n">
         <v>1034.374184443481</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.54</v>
+        <v>-8.67</v>
       </c>
       <c r="L73" t="n">
-        <v>5.92</v>
+        <v>8.91</v>
       </c>
       <c r="M73" t="n">
         <v>1.67</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>11.47</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H74" t="n">
-        <v>1140.3</v>
+        <v>1106</v>
       </c>
       <c r="I74" t="n">
         <v>1138.12402707355</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K74" t="n">
-        <v>9.82</v>
+        <v>6.52</v>
       </c>
       <c r="L74" t="n">
         <v>7.33</v>
@@ -4659,7 +5546,7 @@
         <v>1.92</v>
       </c>
       <c r="N74" t="n">
-        <v>2.54</v>
+        <v>3.01</v>
       </c>
       <c r="O74" t="n">
         <v>4.95</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>7</v>
+      </c>
+      <c r="U74" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>8.43</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H75" t="n">
-        <v>1111.6</v>
+        <v>1164.8</v>
       </c>
       <c r="I75" t="n">
         <v>1155.483917709878</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.51</v>
+        <v>-5.32</v>
       </c>
       <c r="L75" t="n">
         <v>7.14</v>
       </c>
       <c r="M75" t="n">
-        <v>1.35</v>
+        <v>3.99</v>
       </c>
       <c r="N75" t="n">
-        <v>3.81</v>
+        <v>4.79</v>
       </c>
       <c r="O75" t="n">
         <v>-3.01</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>7.74</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H76" t="n">
-        <v>1233.7</v>
+        <v>1192.6</v>
       </c>
       <c r="I76" t="n">
         <v>1203.572653823259</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K76" t="n">
-        <v>5.92</v>
+        <v>2.39</v>
       </c>
       <c r="L76" t="n">
         <v>2.76</v>
       </c>
       <c r="M76" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="N76" t="n">
         <v>4.28</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>8</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H77" t="n">
-        <v>1214.9</v>
+        <v>1240.3</v>
       </c>
       <c r="I77" t="n">
         <v>1236.021869828586</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K77" t="n">
-        <v>-1.87</v>
+        <v>-4</v>
       </c>
       <c r="L77" t="n">
         <v>4.22</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>10.03</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="H78" t="n">
-        <v>1242.2</v>
+        <v>1231.2</v>
       </c>
       <c r="I78" t="n">
         <v>1234.582844183946</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K78" t="n">
-        <v>0.15</v>
+        <v>-0.73</v>
       </c>
       <c r="L78" t="n">
         <v>3.36</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>6.9</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H79" t="n">
-        <v>1292.3</v>
+        <v>1300</v>
       </c>
       <c r="I79" t="n">
         <v>1295.569970572433</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K79" t="n">
-        <v>-4.96</v>
+        <v>-5.59</v>
       </c>
       <c r="L79" t="n">
         <v>5.95</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>6.85</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H80" t="n">
-        <v>1304</v>
+        <v>1265</v>
       </c>
       <c r="I80" t="n">
         <v>1265.274952618126</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K80" t="n">
-        <v>0.31</v>
+        <v>-2.69</v>
       </c>
       <c r="L80" t="n">
         <v>3.82</v>
       </c>
       <c r="M80" t="n">
-        <v>0.91</v>
+        <v>1.76</v>
       </c>
       <c r="N80" t="n">
-        <v>2.04</v>
+        <v>2.99</v>
       </c>
       <c r="O80" t="n">
         <v>0.6</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>7.04</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="H81" t="n">
-        <v>1185.5</v>
+        <v>1260</v>
       </c>
       <c r="I81" t="n">
         <v>1254.652534620884</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K81" t="n">
-        <v>6.28</v>
+        <v>0.4</v>
       </c>
       <c r="L81" t="n">
         <v>3.08</v>
@@ -5058,7 +6029,7 @@
         <v>1.33</v>
       </c>
       <c r="N81" t="n">
-        <v>2.43</v>
+        <v>6.28</v>
       </c>
       <c r="O81" t="n">
         <v>-2.99</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5118,6 +6101,14 @@
       <c r="Q82" t="n">
         <v>3</v>
       </c>
+      <c r="R82" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10076,7 +11067,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="6">
@@ -10086,7 +11077,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -10096,7 +11087,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8">
@@ -10106,7 +11097,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10116,7 +11107,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70.8</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="10">
@@ -10126,7 +11117,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107.1</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="11">
@@ -10166,7 +11157,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.02</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="15">
@@ -10176,7 +11167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.06</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -10186,7 +11177,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.02</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="17">
@@ -10196,7 +11187,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>65.55</v>
+        <v>61.58</v>
       </c>
     </row>
     <row r="18">
@@ -10206,7 +11197,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="19">
@@ -10216,7 +11207,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.48</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="20">
@@ -10226,7 +11217,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.86</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="21">
@@ -10236,7 +11227,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.63</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="22">
@@ -10246,7 +11237,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -10256,7 +11247,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -10266,7 +11257,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="25">
@@ -10276,7 +11267,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.06</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="26">
@@ -10286,7 +11277,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.13</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="27">
@@ -10306,7 +11297,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
